--- a/out/MLP-mamba2_repeat_3_000002.xlsx
+++ b/out/MLP-mamba2_repeat_3_000002.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.990389075499146</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.590389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.590389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.590389075499146</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.590389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.590389075499146</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.590389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.590389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.590389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.590389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.590389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.590389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.590389075499146</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.590389075499146</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.990389075499146</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.590389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.990389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.590389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.590389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.590389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.590389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.990389075499146</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.590389075499146</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.590389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.990389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.590389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.590389075499146</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.590389075499146</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.590389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.590389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.590389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.590389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.990389075499146</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-mamba2_repeat_3_000002.xlsx
+++ b/out/MLP-mamba2_repeat_3_000002.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.4518763352092358</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.990389075499146</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.5557497644722085</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5557497644722085</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-0.4267998384952287</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.590389075499146</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.5557497644722085</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.590389075499146</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5557497644722085</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-0.4267998384952287</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4267998384952287</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.590389075499146</v>
+        <v>1.01143505977739</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.990389075499146</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.8114350597773905</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.590389075499146</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.590389075499146</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5557497644722085</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.990389075499146</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5557497644722085</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.990389075499146</v>
+        <v>0.8114350597773905</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.590389075499146</v>
+        <v>1.01143505977739</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5557497644722085</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.990389075499146</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5557497644722085</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-0.4267998384952287</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.590389075499146</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5557497644722085</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-0.4267998384952287</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4267998384952287</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.590389075499146</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.590389075499146</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5557497644722085</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.590389075499146</v>
+        <v>1.01143505977739</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.590389075499146</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.990389075499146</v>
+        <v>0.4518763352092358</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-mamba2_repeat_3_000002.xlsx
+++ b/out/MLP-mamba2_repeat_3_000002.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4386163651943207</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.4518763352092358</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.6234613060951233</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.0923176106410809</v>
+        <v>-0.58</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.3389216065406799</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.292317610641081</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.3819572925567627</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.437595009803772</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4668188095092773</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.3520456850528717</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.0923176106410809</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.5293031334877014</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.011435059777391</v>
+        <v>-0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.7695196270942688</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.011435059777391</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.2957316339015961</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.292317610641081</v>
+        <v>0.16</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.3905098736286163</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4267998384952287</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3474650382995605</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.0923176106410809</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.501376211643219</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.0923176106410809</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.3431125283241272</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.292317610641081</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.3891695737838745</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.3237663805484772</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.3461389541625977</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.3563920557498932</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.3596838116645813</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4571378827095032</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.2975180447101593</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.343269020318985</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.16</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3953546583652496</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.292317610641081</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.8197755813598633</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.292317610641081</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.3351275324821472</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.292317610641081</v>
+        <v>0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4948084950447083</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.4267998384952287</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.4296357035636902</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.4267998384952287</v>
+        <v>0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.4833560287952423</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.3473778665065765</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.3434074223041534</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.3582615554332733</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.3969234824180603</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.3948353826999664</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.4064156413078308</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.292317610641081</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.5170050859451294</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.011435059777391</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.6813495755195618</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.7305525089137</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.5350651144981384</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.01143505977739</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4775071144104004</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.011435059777391</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.6811502575874329</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.011435059777391</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.7455316185951233</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.7305525089137</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.8833190202713013</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.7305525089137</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.867139458656311</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.7305525089137</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.6279628276824951</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.7305525089137</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.9263322949409485</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.011435059777391</v>
+        <v>-0.16</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.02981084585189819</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.0923176106410809</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.2922028005123138</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.3089850842952728</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.0923176106410809</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.6309359073638916</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.0923176106410809</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.4427386522293091</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.8114350597773905</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.9172114729881287</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.0923176106410809</v>
+        <v>-0.16</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.2651771306991577</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.011435059777391</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.5594448447227478</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.0923176106410809</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.3244185149669647</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.292317610641081</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.4861931800842285</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.0923176106410809</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.6036001443862915</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.0923176106410809</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.3595285415649414</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.011435059777391</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.5085074901580811</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.011435059777391</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.7170745134353638</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.011435059777391</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.4360068440437317</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.011435059777391</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.5717501044273376</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.011435059777391</v>
+        <v>0.3</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.7156835198402405</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.011435059777391</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.4363776445388794</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.292317610641081</v>
+        <v>0.3</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.4224787652492523</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.0923176106410809</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.7149014472961426</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.8114350597773905</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.7571555376052856</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.7305525089137</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.8153806328773499</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.01143505977739</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.3342685997486115</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.292317610641081</v>
+        <v>0.16</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.3227994441986084</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.3956824839115143</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.4206999838352203</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.4055921733379364</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.3242113888263702</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.0923176106410809</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.5522289872169495</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.0923176106410809</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.3768582940101624</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.292317610641081</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.4102172553539276</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4267998384952287</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3616029322147369</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.3031935095787048</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.3807620704174042</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.3959012627601624</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.4498705863952637</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.4382098913192749</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.0923176106410809</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.529120922088623</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.292317610641081</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4792114496231079</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.292317610641081</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.4694817960262299</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4267998384952287</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3117305934429169</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4267998384952287</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3570513129234314</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.0923176106410809</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.5362740755081177</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.292317610641081</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.3155180513858795</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.011435059777391</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.6185553073883057</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.292317610641081</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.4845106899738312</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.292317610641081</v>
+        <v>0.3</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4598324298858643</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.3</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3438721001148224</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3147030770778656</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.331107497215271</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.3607169389724731</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.3521526157855988</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3675857186317444</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.3331616222858429</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.4175574779510498</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.3361276984214783</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.16</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3603812754154205</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.16</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.4268592894077301</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.3381253182888031</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.3397484421730042</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.3436077833175659</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.3390798568725586</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3711012303829193</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.4139635562896729</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3377653658390045</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3739783465862274</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.16</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.3012721836566925</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.16</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.4471560418605804</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.4988312125205994</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.3683888018131256</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4256664514541626</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.292317610641081</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.6087514162063599</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.011435059777391</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.6141790747642517</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.7305525089137</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.8960078358650208</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.01143505977739</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.3215524554252625</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.011435059777391</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.7761359810829163</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.292317610641081</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.44803187251091</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.292317610641081</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.4179284572601318</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.4380748569965363</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.460638165473938</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.0923176106410809</v>
+        <v>0.7900000000000003</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
+        <v>0.7862583994865417</v>
+      </c>
+      <c r="JB126" t="n">
         <v>1</v>
-      </c>
-      <c r="JB126" t="n">
-        <v>0.4518763352092358</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-mamba2_repeat_3_000002.xlsx
+++ b/out/MLP-mamba2_repeat_3_000002.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.4386163651943207</v>
+        <v>0.438616544008255</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.4399999999999999</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.6234613060951233</v>
+        <v>0.623461902141571</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.58</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.3389216065406799</v>
+        <v>0.3389219641685486</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.7199999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.3819572925567627</v>
+        <v>0.3819575309753418</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.5799999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.437595009803772</v>
+        <v>0.4375954568386078</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.8599999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.4668188095092773</v>
+        <v>0.4668192863464355</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.5799999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.3520456850528717</v>
+        <v>0.3520459234714508</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.3</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.5293031334877014</v>
+        <v>0.5293037891387939</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.3</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.7695196270942688</v>
+        <v>0.7695204615592957</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.4399999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.2957316339015961</v>
+        <v>0.295732319355011</v>
       </c>
       <c r="JB11" t="n">
         <v>0.16</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.3905098736286163</v>
+        <v>0.3905101418495178</v>
       </c>
       <c r="JB12" t="n">
         <v>0.02000000000000007</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.3474650382995605</v>
+        <v>0.347464919090271</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.8599999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.501376211643219</v>
+        <v>0.5013766288757324</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.8599999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.3431125283241272</v>
+        <v>0.3431128263473511</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.8599999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.3891695737838745</v>
+        <v>0.3891696631908417</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.8599999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.3237663805484772</v>
+        <v>0.3237666189670563</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.9999999999999998</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.3461389541625977</v>
+        <v>0.3461391627788544</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.9999999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.3563920557498932</v>
+        <v>0.3563924133777618</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.7199999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.3596838116645813</v>
+        <v>0.3596839904785156</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.7199999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.4571378827095032</v>
+        <v>0.4571381211280823</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.1199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.2975180447101593</v>
+        <v>0.297518402338028</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.1199999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.343269020318985</v>
+        <v>0.3432691693305969</v>
       </c>
       <c r="JB23" t="n">
         <v>0.16</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.3953546583652496</v>
+        <v>0.395354688167572</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.1199999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.8197755813598633</v>
+        <v>0.8197762370109558</v>
       </c>
       <c r="JB25" t="n">
         <v>0.1600000000000001</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.3351275324821472</v>
+        <v>0.3351282775402069</v>
       </c>
       <c r="JB26" t="n">
         <v>0.3</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.4948084950447083</v>
+        <v>0.4948091208934784</v>
       </c>
       <c r="JB27" t="n">
         <v>0.5799999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.4296357035636902</v>
+        <v>0.4296361804008484</v>
       </c>
       <c r="JB28" t="n">
         <v>0.3</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.4833560287952423</v>
+        <v>0.4833564758300781</v>
       </c>
       <c r="JB29" t="n">
         <v>0.3</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.3473778665065765</v>
+        <v>0.3473781645298004</v>
       </c>
       <c r="JB30" t="n">
         <v>0.02000000000000007</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.3434074223041534</v>
+        <v>0.3434075713157654</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.7199999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.3582615554332733</v>
+        <v>0.358261913061142</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.9999999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.3969234824180603</v>
+        <v>0.3969235718250275</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.9999999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.3948353826999664</v>
+        <v>0.3948354721069336</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.7199999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.4064156413078308</v>
+        <v>0.4064159095287323</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.4399999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.5170050859451294</v>
+        <v>0.517005443572998</v>
       </c>
       <c r="JB36" t="n">
         <v>0.4399999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.6813495755195618</v>
+        <v>0.6813503503799438</v>
       </c>
       <c r="JB37" t="n">
         <v>0.7199999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.5350651144981384</v>
+        <v>0.5350658893585205</v>
       </c>
       <c r="JB38" t="n">
         <v>0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.4775071144104004</v>
+        <v>0.4775075316429138</v>
       </c>
       <c r="JB39" t="n">
         <v>0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.6811502575874329</v>
+        <v>0.6811512112617493</v>
       </c>
       <c r="JB40" t="n">
         <v>0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.7455316185951233</v>
+        <v>0.7455326318740845</v>
       </c>
       <c r="JB41" t="n">
         <v>0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.8833190202713013</v>
+        <v>0.883319616317749</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.867139458656311</v>
+        <v>0.867138147354126</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.6279628276824951</v>
+        <v>0.6279609799385071</v>
       </c>
       <c r="JB44" t="n">
         <v>0.7199999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.9263322949409485</v>
+        <v>0.9263312816619873</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.16</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.02981084585189819</v>
+        <v>0.02981078252196312</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.4399999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.2922028005123138</v>
+        <v>0.2922023832798004</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.4399999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.3089850842952728</v>
+        <v>0.308986634016037</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.7199999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.6309359073638916</v>
+        <v>0.6309348940849304</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.4399999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.4427386522293091</v>
+        <v>0.4427399635314941</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.4399999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.9172114729881287</v>
+        <v>0.9172106981277466</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.16</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.2651771306991577</v>
+        <v>0.2651760280132294</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.4399999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.5594448447227478</v>
+        <v>0.5594439506530762</v>
       </c>
       <c r="JB53" t="n">
         <v>0.1600000000000001</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.3244185149669647</v>
+        <v>0.3244200050830841</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.5799999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.4861931800842285</v>
+        <v>0.4861940741539001</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.5799999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.6036001443862915</v>
+        <v>0.6036014556884766</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.7199999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.3595285415649414</v>
+        <v>0.3595291078090668</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.4399999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.5085074901580811</v>
+        <v>0.5085080862045288</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.4399999999999999</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.7170745134353638</v>
+        <v>0.7170756459236145</v>
       </c>
       <c r="JB59" t="n">
         <v>0.1600000000000001</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.4360068440437317</v>
+        <v>0.4360087215900421</v>
       </c>
       <c r="JB60" t="n">
         <v>0.4399999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.5717501044273376</v>
+        <v>0.5717511177062988</v>
       </c>
       <c r="JB61" t="n">
         <v>0.3</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.7156835198402405</v>
+        <v>0.7156825065612793</v>
       </c>
       <c r="JB62" t="n">
         <v>0.02000000000000007</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.4363776445388794</v>
+        <v>0.4363790452480316</v>
       </c>
       <c r="JB63" t="n">
         <v>0.3</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.4224787652492523</v>
+        <v>0.4224794209003448</v>
       </c>
       <c r="JB64" t="n">
         <v>0.4399999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.7149014472961426</v>
+        <v>0.7149026393890381</v>
       </c>
       <c r="JB65" t="n">
         <v>0.4399999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.7571555376052856</v>
+        <v>0.7571542859077454</v>
       </c>
       <c r="JB66" t="n">
         <v>0.4399999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.8153806328773499</v>
+        <v>0.8153790831565857</v>
       </c>
       <c r="JB67" t="n">
         <v>0.4399999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.3342685997486115</v>
+        <v>0.3342672884464264</v>
       </c>
       <c r="JB68" t="n">
         <v>0.16</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.3227994441986084</v>
+        <v>0.3228009343147278</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.7199999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.3956824839115143</v>
+        <v>0.395683616399765</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.4206999838352203</v>
+        <v>0.4207008183002472</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.4055921733379364</v>
+        <v>0.4055929780006409</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.7199999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.3242113888263702</v>
+        <v>0.3242117762565613</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.7199999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.5522289872169495</v>
+        <v>0.552229642868042</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.7199999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.3768582940101624</v>
+        <v>0.376858651638031</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.7199999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.3616029322147369</v>
+        <v>0.3616029918193817</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.3031935095787048</v>
+        <v>0.303193598985672</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.3807620704174042</v>
+        <v>0.380762130022049</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.3959012627601624</v>
+        <v>0.39590123295784</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.4498705863952637</v>
+        <v>0.4498706161975861</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.7199999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.4382098913192749</v>
+        <v>0.4382099211215973</v>
       </c>
       <c r="JB82" t="n">
         <v>0.02000000000000007</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.529120922088623</v>
+        <v>0.5291211009025574</v>
       </c>
       <c r="JB83" t="n">
         <v>0.02000000000000007</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.4792114496231079</v>
+        <v>0.4792115092277527</v>
       </c>
       <c r="JB84" t="n">
         <v>0.02000000000000007</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.4694817960262299</v>
+        <v>0.4694818556308746</v>
       </c>
       <c r="JB85" t="n">
         <v>0.02000000000000007</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.3570513129234314</v>
+        <v>0.3570512533187866</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.1199999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.3155180513858795</v>
+        <v>0.3155183792114258</v>
       </c>
       <c r="JB89" t="n">
         <v>0.4399999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.6185553073883057</v>
+        <v>0.6185563802719116</v>
       </c>
       <c r="JB90" t="n">
         <v>0.5799999999999998</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.4845106899738312</v>
+        <v>0.4845108687877655</v>
       </c>
       <c r="JB91" t="n">
         <v>0.3</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.4598324298858643</v>
+        <v>0.459832489490509</v>
       </c>
       <c r="JB92" t="n">
         <v>0.3</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.3438721001148224</v>
+        <v>0.343872606754303</v>
       </c>
       <c r="JB93" t="n">
         <v>0.02000000000000007</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.3147030770778656</v>
+        <v>0.3147032558917999</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.8599999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.331107497215271</v>
+        <v>0.3311075270175934</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.9999999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.3607169389724731</v>
+        <v>0.360716849565506</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.9999999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.3521526157855988</v>
+        <v>0.3521531522274017</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.9999999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.3675857186317444</v>
+        <v>0.3675858378410339</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.7199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.3331616222858429</v>
+        <v>0.3331618010997772</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.7199999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.4175574779510498</v>
+        <v>0.417557418346405</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.3361276984214783</v>
+        <v>0.3361280262470245</v>
       </c>
       <c r="JB101" t="n">
         <v>0.16</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.3603812754154205</v>
+        <v>0.360381156206131</v>
       </c>
       <c r="JB102" t="n">
         <v>0.16</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.4268592894077301</v>
+        <v>0.4268593192100525</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.1199999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.3381253182888031</v>
+        <v>0.3381255567073822</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.1199999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.3397484421730042</v>
+        <v>0.3397485315799713</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.7199999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.3436077833175659</v>
+        <v>0.3436079919338226</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.3390798568725586</v>
+        <v>0.3390801846981049</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.3711012303829193</v>
+        <v>0.3711013197898865</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.7199999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.4139635562896729</v>
+        <v>0.4139635264873505</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.7199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.3377653658390045</v>
+        <v>0.3377655148506165</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.7199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.3739783465862274</v>
+        <v>0.3739782869815826</v>
       </c>
       <c r="JB111" t="n">
         <v>0.16</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.3012721836566925</v>
+        <v>0.3012725710868835</v>
       </c>
       <c r="JB112" t="n">
         <v>0.16</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.4471560418605804</v>
+        <v>0.4471563398838043</v>
       </c>
       <c r="JB113" t="n">
         <v>0.1600000000000001</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.4988312125205994</v>
+        <v>0.4988315105438232</v>
       </c>
       <c r="JB114" t="n">
         <v>0.4399999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.3683888018131256</v>
+        <v>0.3683890104293823</v>
       </c>
       <c r="JB115" t="n">
         <v>0.7199999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.4256664514541626</v>
+        <v>0.4256667494773865</v>
       </c>
       <c r="JB116" t="n">
         <v>0.7199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.6087514162063599</v>
+        <v>0.6087522506713867</v>
       </c>
       <c r="JB117" t="n">
         <v>0.7199999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.6141790747642517</v>
+        <v>0.6141802072525024</v>
       </c>
       <c r="JB118" t="n">
         <v>0.7199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.8960078358650208</v>
+        <v>0.8960081934928894</v>
       </c>
       <c r="JB119" t="n">
         <v>0.7199999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.3215524554252625</v>
+        <v>0.321553647518158</v>
       </c>
       <c r="JB120" t="n">
         <v>0.5799999999999998</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.7761359810829163</v>
+        <v>0.7761369347572327</v>
       </c>
       <c r="JB121" t="n">
         <v>0.4399999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.44803187251091</v>
+        <v>0.4480329155921936</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.3</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.4179284572601318</v>
+        <v>0.4179292917251587</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.02000000000000007</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.4380748569965363</v>
+        <v>0.4380759596824646</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.02000000000000007</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.460638165473938</v>
+        <v>0.4606388807296753</v>
       </c>
       <c r="JB125" t="n">
         <v>0.7900000000000003</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.7862583994865417</v>
+        <v>0.7862590551376343</v>
       </c>
       <c r="JB126" t="n">
         <v>1</v>
